--- a/StructureDefinition-mii-pr-icu-ect-substituatvolumen.xlsx
+++ b/StructureDefinition-mii-pr-icu-ect-substituatvolumen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ballot.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T06:46:19+00:00</t>
+    <t>2026-09-15T22:20:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-icu-ect-substituatvolumen.xlsx
+++ b/StructureDefinition-mii-pr-icu-ect-substituatvolumen.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T22:20:02+00:00</t>
+    <t>2026-09-17T12:17:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
